--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3629-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3629-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{990FB4C3-2228-49AC-BA4F-7C2320327049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0636A1F8-254C-49BC-BC38-BC96C9BE237C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FFA5AD41-8A50-42CC-9552-BDD00FCACB65}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F014E742-C8E8-46B1-9B76-89FB30BE6411}"/>
   </bookViews>
   <sheets>
     <sheet name="3629-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1493,24 +1493,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CA9DB44-E4B9-4614-98FB-7ECF16173B3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67DE28C0-D600-4F35-8FCE-2D6C8DE694B9}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.77734375" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10.125" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="10.125" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="7" max="9" width="10.125" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="13" width="10.125" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1568,7 +1568,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1664,7 +1664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2019</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2018</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2017</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2016</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2015</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2014</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2013</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2012</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2011</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2010</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2009</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
         <v>50</v>
       </c>
